--- a/autoemx/data/Xray_lines/LineWeights_mod.xlsx
+++ b/autoemx/data/Xray_lines/LineWeights_mod.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Andrea_1/Desktop/Work/Codes/EDX/lib/Xray_lines/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Andrea_1/Desktop/Work/Codes/Repositories/AutoEMXSp/autoemx/data/Xray_lines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0605BA5F-F7DC-7A44-8491-906E45B479C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A589FF6-9F09-C24D-9739-3A841E9FC5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51060" yWindow="5140" windowWidth="29920" windowHeight="18660" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
+    <workbookView xWindow="40140" yWindow="2800" windowWidth="29920" windowHeight="18660" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
   </bookViews>
   <sheets>
     <sheet name="LineWeights" sheetId="1" r:id="rId1"/>
@@ -15028,10 +15028,10 @@
         <v>0</v>
       </c>
       <c r="BE60" s="1">
-        <v>3.9800000000000002E-2</v>
+        <v>4.3790000000000003E-2</v>
       </c>
       <c r="BF60" s="1">
-        <v>7.2499999999999995E-2</v>
+        <v>0.28420000000000001</v>
       </c>
       <c r="BG60" s="1">
         <v>0</v>
@@ -15058,7 +15058,7 @@
         <v>0</v>
       </c>
       <c r="BO60" s="1">
-        <v>0.115</v>
+        <v>0.4773</v>
       </c>
       <c r="BP60" s="1">
         <v>0</v>
@@ -15067,22 +15067,22 @@
         <v>9.9599999999999992E-4</v>
       </c>
       <c r="BR60" s="1">
-        <v>0.107</v>
+        <v>1.377</v>
       </c>
       <c r="BS60" s="1">
-        <v>0.76500000000000001</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="BT60" s="1">
         <v>7.6100000000000007E-5</v>
       </c>
       <c r="BU60" s="1">
+        <v>1</v>
+      </c>
+      <c r="BV60" s="1">
         <v>8.4500000000000006E-2</v>
       </c>
-      <c r="BV60" s="1">
-        <v>1</v>
-      </c>
       <c r="BW60" s="1">
-        <v>0.26200000000000001</v>
+        <v>1.716</v>
       </c>
       <c r="BX60">
         <v>0</v>

--- a/autoemx/data/Xray_lines/LineWeights_mod.xlsx
+++ b/autoemx/data/Xray_lines/LineWeights_mod.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Andrea_1/Desktop/Work/Codes/Repositories/AutoEMXSp/autoemx/data/Xray_lines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A589FF6-9F09-C24D-9739-3A841E9FC5D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36B401C-1CF7-1F49-863A-DEF5AD355699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40140" yWindow="2800" windowWidth="29920" windowHeight="18660" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
+    <workbookView xWindow="39080" yWindow="9040" windowWidth="29920" windowHeight="18660" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
   </bookViews>
   <sheets>
     <sheet name="LineWeights" sheetId="1" r:id="rId1"/>
@@ -14953,7 +14953,7 @@
         <v>0</v>
       </c>
       <c r="AF60" s="1">
-        <v>0.495</v>
+        <v>0.48499999999999999</v>
       </c>
       <c r="AG60" s="1">
         <v>3.9599999999999998E-4</v>
@@ -14995,7 +14995,7 @@
         <v>3.2699999999999999E-3</v>
       </c>
       <c r="AT60" s="1">
-        <v>0.111</v>
+        <v>9.2520000000000005E-2</v>
       </c>
       <c r="AU60" s="1">
         <v>0.1</v>
@@ -15028,10 +15028,10 @@
         <v>0</v>
       </c>
       <c r="BE60" s="1">
-        <v>4.3790000000000003E-2</v>
+        <v>0.1968</v>
       </c>
       <c r="BF60" s="1">
-        <v>0.28420000000000001</v>
+        <v>0.3049</v>
       </c>
       <c r="BG60" s="1">
         <v>0</v>
@@ -15058,7 +15058,7 @@
         <v>0</v>
       </c>
       <c r="BO60" s="1">
-        <v>0.4773</v>
+        <v>0.46189999999999998</v>
       </c>
       <c r="BP60" s="1">
         <v>0</v>
@@ -15070,7 +15070,7 @@
         <v>1.377</v>
       </c>
       <c r="BS60" s="1">
-        <v>0.14799999999999999</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="BT60" s="1">
         <v>7.6100000000000007E-5</v>
@@ -15082,7 +15082,7 @@
         <v>8.4500000000000006E-2</v>
       </c>
       <c r="BW60" s="1">
-        <v>1.716</v>
+        <v>3.714</v>
       </c>
       <c r="BX60">
         <v>0</v>
@@ -17007,14 +17007,14 @@
       <c r="Q69" s="1">
         <v>0</v>
       </c>
-      <c r="R69" s="1">
-        <v>8.7100000000000007E-3</v>
-      </c>
-      <c r="S69" s="1">
-        <v>7.7200000000000001E-4</v>
-      </c>
-      <c r="T69" s="1">
-        <v>4.8500000000000001E-2</v>
+      <c r="R69">
+        <v>6.9709999999999998E-3</v>
+      </c>
+      <c r="S69">
+        <v>2.2350000000000001E-4</v>
+      </c>
+      <c r="T69">
+        <v>3.5310000000000001E-2</v>
       </c>
       <c r="U69" s="1">
         <v>0</v>
@@ -17049,8 +17049,8 @@
       <c r="AE69" s="1">
         <v>0</v>
       </c>
-      <c r="AF69" s="1">
-        <v>0.50800000000000001</v>
+      <c r="AF69">
+        <v>0.41520000000000001</v>
       </c>
       <c r="AG69" s="1">
         <v>6.7500000000000004E-4</v>
@@ -17088,14 +17088,14 @@
       <c r="AR69" s="1">
         <v>0</v>
       </c>
-      <c r="AS69" s="1">
-        <v>1.06E-2</v>
-      </c>
-      <c r="AT69" s="1">
-        <v>0.105</v>
-      </c>
-      <c r="AU69" s="1">
-        <v>6.2799999999999995E-2</v>
+      <c r="AS69">
+        <v>3.0690000000000001E-3</v>
+      </c>
+      <c r="AT69">
+        <v>8.4029999999999994E-2</v>
+      </c>
+      <c r="AU69">
+        <v>5.1319999999999998E-2</v>
       </c>
       <c r="AV69" s="1">
         <v>0</v>
@@ -17127,8 +17127,8 @@
       <c r="BE69" s="1">
         <v>3.1600000000000003E-2</v>
       </c>
-      <c r="BF69" s="1">
-        <v>6.9900000000000004E-2</v>
+      <c r="BF69">
+        <v>7.5490000000000002E-2</v>
       </c>
       <c r="BG69" s="1">
         <v>0</v>
@@ -17154,8 +17154,8 @@
       <c r="BN69" s="1">
         <v>0</v>
       </c>
-      <c r="BO69" s="1">
-        <v>9.6299999999999997E-2</v>
+      <c r="BO69">
+        <v>0.16600000000000001</v>
       </c>
       <c r="BP69" s="1">
         <v>0</v>
@@ -17164,10 +17164,10 @@
         <v>5.4699999999999996E-4</v>
       </c>
       <c r="BR69" s="1">
-        <v>0.99099999999999999</v>
-      </c>
-      <c r="BS69" s="1">
-        <v>7.4800000000000005E-2</v>
+        <v>1.5680000000000001</v>
+      </c>
+      <c r="BS69">
+        <v>0.10970000000000001</v>
       </c>
       <c r="BT69" s="1">
         <v>1.85E-4</v>
@@ -17178,8 +17178,8 @@
       <c r="BV69" s="1">
         <v>1</v>
       </c>
-      <c r="BW69" s="1">
-        <v>0.45</v>
+      <c r="BW69">
+        <v>0.66020000000000001</v>
       </c>
       <c r="BX69">
         <v>0</v>

--- a/autoemx/data/Xray_lines/LineWeights_mod.xlsx
+++ b/autoemx/data/Xray_lines/LineWeights_mod.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Andrea_1/Desktop/Work/Codes/Repositories/AutoEMXSp/autoemx/data/Xray_lines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36B401C-1CF7-1F49-863A-DEF5AD355699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3877B7-9FF7-C04F-A7E4-D4C0BFA62BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39080" yWindow="9040" windowWidth="29920" windowHeight="18660" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
+    <workbookView xWindow="440" yWindow="700" windowWidth="33560" windowHeight="20500" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
   </bookViews>
   <sheets>
     <sheet name="LineWeights" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>// K-L3</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>N5-N6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -13871,8 +13874,8 @@
       <c r="BG55">
         <v>0</v>
       </c>
-      <c r="BH55">
-        <v>0</v>
+      <c r="BH55" t="s">
+        <v>77</v>
       </c>
       <c r="BI55">
         <v>0</v>
@@ -15149,8 +15152,8 @@
       <c r="S61" s="1">
         <v>4.9700000000000005E-4</v>
       </c>
-      <c r="T61" s="1">
-        <v>4.6600000000000003E-2</v>
+      <c r="T61">
+        <v>4.086E-2</v>
       </c>
       <c r="U61" s="1">
         <v>0</v>
@@ -15185,8 +15188,8 @@
       <c r="AE61" s="1">
         <v>0</v>
       </c>
-      <c r="AF61" s="1">
-        <v>0.48899999999999999</v>
+      <c r="AF61">
+        <v>0.44969999999999999</v>
       </c>
       <c r="AG61" s="1">
         <v>4.9700000000000005E-4</v>
@@ -15227,11 +15230,11 @@
       <c r="AS61" s="1">
         <v>4.2700000000000004E-3</v>
       </c>
-      <c r="AT61" s="1">
-        <v>0.109</v>
-      </c>
-      <c r="AU61" s="1">
-        <v>9.8699999999999996E-2</v>
+      <c r="AT61">
+        <v>8.7010000000000004E-2</v>
+      </c>
+      <c r="AU61">
+        <v>9.078E-2</v>
       </c>
       <c r="AV61" s="1">
         <v>0</v>
@@ -15260,11 +15263,11 @@
       <c r="BD61" s="1">
         <v>0</v>
       </c>
-      <c r="BE61" s="1">
+      <c r="BE61">
         <v>3.56E-2</v>
       </c>
-      <c r="BF61" s="1">
-        <v>7.2900000000000006E-2</v>
+      <c r="BF61">
+        <v>0.20649999999999999</v>
       </c>
       <c r="BG61" s="1">
         <v>0</v>
@@ -15290,7 +15293,7 @@
       <c r="BN61" s="1">
         <v>0</v>
       </c>
-      <c r="BO61" s="1">
+      <c r="BO61">
         <v>0.152</v>
       </c>
       <c r="BP61" s="1">
@@ -15302,20 +15305,20 @@
       <c r="BR61" s="1">
         <v>0.63500000000000001</v>
       </c>
-      <c r="BS61" s="1">
-        <v>1</v>
+      <c r="BS61">
+        <v>0.42409999999999998</v>
       </c>
       <c r="BT61" s="1">
         <v>1.17E-4</v>
       </c>
       <c r="BU61" s="1">
-        <v>0.42099999999999999</v>
+        <v>1</v>
       </c>
       <c r="BV61" s="1">
         <v>0.17</v>
       </c>
-      <c r="BW61" s="1">
-        <v>0.34899999999999998</v>
+      <c r="BW61">
+        <v>1.2150000000000001</v>
       </c>
       <c r="BX61">
         <v>0</v>

--- a/autoemx/data/Xray_lines/LineWeights_mod.xlsx
+++ b/autoemx/data/Xray_lines/LineWeights_mod.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Andrea_1/Desktop/Work/Codes/Repositories/AutoEMXSp/autoemx/data/Xray_lines/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3877B7-9FF7-C04F-A7E4-D4C0BFA62BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A5D70D-B95B-BD4D-AC0B-75608A006CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="440" yWindow="700" windowWidth="33560" windowHeight="20500" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
+    <workbookView xWindow="37660" yWindow="600" windowWidth="48760" windowHeight="26700" xr2:uid="{69DD2CB1-1C64-1C40-B86B-BA2360568088}"/>
   </bookViews>
   <sheets>
     <sheet name="LineWeights" sheetId="1" r:id="rId1"/>
@@ -32,10 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
-  <si>
-    <t>// K-L3</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>K-L2</t>
   </si>
@@ -265,7 +262,7 @@
     <t>N5-N6</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>K-L3</t>
   </si>
 </sst>
 </file>
@@ -1116,235 +1113,235 @@
   <sheetData>
     <row r="1" spans="1:77" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:77" x14ac:dyDescent="0.2">
@@ -13874,8 +13871,8 @@
       <c r="BG55">
         <v>0</v>
       </c>
-      <c r="BH55" t="s">
-        <v>77</v>
+      <c r="BH55">
+        <v>0</v>
       </c>
       <c r="BI55">
         <v>0</v>
